--- a/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
+++ b/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\UIRI_Projects\Database _Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\uiri-ims\documentation\srs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD0E818-869C-49EF-97B2-B37EA541CA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A683749-4458-47F5-801E-132360253C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1270,6 +1270,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAB79439-80C4-D409-B34F-B53D30158778}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2379,7 +2433,7 @@
       <c r="BK10" s="42"/>
       <c r="BL10" s="42"/>
     </row>
-    <row r="11" spans="1:64" s="30" customFormat="1" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19"/>
       <c r="B11" s="57" t="s">
         <v>24</v>
@@ -3162,7 +3216,7 @@
         <v>27</v>
       </c>
       <c r="D21" s="110">
-        <v>0.45</v>
+        <v>0.97</v>
       </c>
       <c r="E21" s="72">
         <v>46202</v>
@@ -3241,7 +3295,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="72">
         <v>46203</v>
@@ -3320,7 +3374,7 @@
         <v>36</v>
       </c>
       <c r="D23" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="72">
         <v>46203</v>
@@ -4781,7 +4835,7 @@
       <c r="BK41" s="42"/>
       <c r="BL41" s="42"/>
     </row>
-    <row r="42" spans="1:64" s="30" customFormat="1" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19"/>
       <c r="B42" s="97" t="s">
         <v>61</v>
@@ -5309,7 +5363,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B0389232-4C98-4A03-AD0E-39F63BAD1F53}</x14:id>
+          <x14:id>{DACA9343-D7F3-4072-9D5A-1E06B289427B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5351,14 +5405,16 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B0389232-4C98-4A03-AD0E-39F63BAD1F53}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+          <x14:cfRule type="dataBar" id="{DACA9343-D7F3-4072-9D5A-1E06B289427B}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
               </x14:cfvo>
               <x14:cfvo type="num">
                 <xm:f>1</xm:f>
               </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
           <x14:cfRule type="dataBar" id="{B0389232-4C98-4A03-AD0E-39F63BAD1F53}">

--- a/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
+++ b/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\uiri-ims\documentation\srs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A683749-4458-47F5-801E-132360253C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517C656C-7AC6-476C-8E0C-7B41D7608F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -115,9 +115,6 @@
     <t>Project Start:</t>
   </si>
   <si>
-    <t>Database Project Team</t>
-  </si>
-  <si>
     <t>Today:</t>
   </si>
   <si>
@@ -320,6 +317,9 @@
   </si>
   <si>
     <t>University</t>
+  </si>
+  <si>
+    <t>Database Project Team:</t>
   </si>
 </sst>
 </file>
@@ -1324,6 +1324,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50619A7C-F9EC-A740-01A0-41705A2ACF5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1593,11 +1647,11 @@
     </row>
     <row r="3" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="C3"/>
       <c r="D3" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="129">
         <v>46201</v>
@@ -1606,11 +1660,11 @@
     </row>
     <row r="4" spans="1:64" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4"/>
       <c r="D4" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="20">
         <v>1</v>
@@ -2207,7 +2261,7 @@
     <row r="8" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A8" s="19"/>
       <c r="B8" s="50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="51"/>
       <c r="D8" s="53"/>
@@ -2278,10 +2332,10 @@
     <row r="9" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19"/>
       <c r="B9" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="58" t="s">
         <v>20</v>
-      </c>
-      <c r="C9" s="58" t="s">
-        <v>21</v>
       </c>
       <c r="D9" s="110">
         <v>1</v>
@@ -2357,10 +2411,10 @@
     <row r="10" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19"/>
       <c r="B10" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="58" t="s">
         <v>22</v>
-      </c>
-      <c r="C10" s="58" t="s">
-        <v>23</v>
       </c>
       <c r="D10" s="110">
         <v>1</v>
@@ -2436,10 +2490,10 @@
     <row r="11" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19"/>
       <c r="B11" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="58" t="s">
         <v>24</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>25</v>
       </c>
       <c r="D11" s="110">
         <v>1</v>
@@ -2515,10 +2569,10 @@
     <row r="12" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19"/>
       <c r="B12" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="58" t="s">
         <v>26</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>27</v>
       </c>
       <c r="D12" s="110">
         <v>1</v>
@@ -2594,10 +2648,10 @@
     <row r="13" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19"/>
       <c r="B13" s="57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="110">
         <v>1</v>
@@ -2673,7 +2727,7 @@
     <row r="14" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19"/>
       <c r="B14" s="61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="62"/>
       <c r="D14" s="105"/>
@@ -2744,10 +2798,10 @@
     <row r="15" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19"/>
       <c r="B15" s="67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" s="110">
         <v>1</v>
@@ -2823,13 +2877,13 @@
     <row r="16" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="68" t="s">
-        <v>32</v>
-      </c>
       <c r="D16" s="110">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E16" s="63">
         <v>46195</v>
@@ -2902,10 +2956,10 @@
     <row r="17" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19"/>
       <c r="B17" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="68" t="s">
         <v>33</v>
-      </c>
-      <c r="C17" s="68" t="s">
-        <v>34</v>
       </c>
       <c r="D17" s="110">
         <v>1</v>
@@ -2981,10 +3035,10 @@
     <row r="18" spans="1:64" s="30" customFormat="1" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
       <c r="B18" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="68" t="s">
         <v>35</v>
-      </c>
-      <c r="C18" s="68" t="s">
-        <v>36</v>
       </c>
       <c r="D18" s="110">
         <v>1</v>
@@ -3060,10 +3114,10 @@
     <row r="19" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19"/>
       <c r="B19" s="67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="110">
         <v>0.85</v>
@@ -3139,7 +3193,7 @@
     <row r="20" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19"/>
       <c r="B20" s="70" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" s="71"/>
       <c r="D20" s="106"/>
@@ -3210,13 +3264,13 @@
     <row r="21" spans="1:64" s="30" customFormat="1" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A21" s="19"/>
       <c r="B21" s="76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" s="77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" s="110">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="E21" s="72">
         <v>46202</v>
@@ -3289,10 +3343,10 @@
     <row r="22" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19"/>
       <c r="B22" s="76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" s="110">
         <v>1</v>
@@ -3368,10 +3422,10 @@
     <row r="23" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A23" s="19"/>
       <c r="B23" s="76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23" s="110">
         <v>1</v>
@@ -3447,13 +3501,13 @@
     <row r="24" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A24" s="19"/>
       <c r="B24" s="76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="72">
         <v>46205</v>
@@ -3526,13 +3580,13 @@
     <row r="25" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A25" s="19"/>
       <c r="B25" s="76" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="110">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E25" s="72">
         <v>46207</v>
@@ -3605,7 +3659,7 @@
     <row r="26" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A26" s="19"/>
       <c r="B26" s="79" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" s="80"/>
       <c r="D26" s="107"/>
@@ -3676,13 +3730,13 @@
     <row r="27" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A27" s="19"/>
       <c r="B27" s="85" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" s="86" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="81">
         <v>46209</v>
@@ -3755,13 +3809,13 @@
     <row r="28" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A28" s="19"/>
       <c r="B28" s="85" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="86" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="81">
         <v>46210</v>
@@ -3834,13 +3888,13 @@
     <row r="29" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19"/>
       <c r="B29" s="85" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="86" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" s="110">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="E29" s="81">
         <v>46211</v>
@@ -3913,13 +3967,13 @@
     <row r="30" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19"/>
       <c r="B30" s="85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="86" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D30" s="110">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E30" s="81">
         <v>46212</v>
@@ -3992,13 +4046,13 @@
     <row r="31" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19"/>
       <c r="B31" s="85" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" s="86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="110">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E31" s="81">
         <v>46213</v>
@@ -4071,7 +4125,7 @@
     <row r="32" spans="1:64" s="30" customFormat="1" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A32" s="19"/>
       <c r="B32" s="50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="108"/>
@@ -4142,10 +4196,10 @@
     <row r="33" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A33" s="19"/>
       <c r="B33" s="57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33" s="110">
         <v>0</v>
@@ -4221,10 +4275,10 @@
     <row r="34" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A34" s="19"/>
       <c r="B34" s="57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="58" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D34" s="110">
         <v>0</v>
@@ -4300,10 +4354,10 @@
     <row r="35" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A35" s="19"/>
       <c r="B35" s="57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D35" s="110">
         <v>0</v>
@@ -4379,10 +4433,10 @@
     <row r="36" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A36" s="19"/>
       <c r="B36" s="57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D36" s="110">
         <v>0</v>
@@ -4458,10 +4512,10 @@
     <row r="37" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A37" s="19"/>
       <c r="B37" s="57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" s="58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D37" s="110">
         <v>0</v>
@@ -4536,7 +4590,7 @@
     <row r="38" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A38" s="19"/>
       <c r="B38" s="90" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38" s="94"/>
       <c r="D38" s="109"/>
@@ -4604,10 +4658,10 @@
     <row r="39" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19"/>
       <c r="B39" s="97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" s="91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" s="110">
         <v>0</v>
@@ -4682,10 +4736,10 @@
     <row r="40" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19"/>
       <c r="B40" s="99" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="91" t="s">
         <v>58</v>
-      </c>
-      <c r="C40" s="91" t="s">
-        <v>59</v>
       </c>
       <c r="D40" s="110">
         <v>0</v>
@@ -4760,10 +4814,10 @@
     <row r="41" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19"/>
       <c r="B41" s="97" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C41" s="91" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D41" s="110">
         <v>0</v>
@@ -4838,10 +4892,10 @@
     <row r="42" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19"/>
       <c r="B42" s="97" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42" s="91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D42" s="110">
         <v>0</v>
@@ -4916,10 +4970,10 @@
     <row r="43" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A43" s="19"/>
       <c r="B43" s="97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" s="91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D43" s="110">
         <v>0</v>
@@ -5449,31 +5503,31 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1"/>
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="104">
         <v>46188</v>
@@ -5481,63 +5535,63 @@
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
         <v>69</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="7" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="7" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>13</v>

--- a/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
+++ b/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\uiri-ims\documentation\srs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517C656C-7AC6-476C-8E0C-7B41D7608F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259534EA-6937-4B31-9B8D-E5468C435218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1378,6 +1378,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94C83E0B-9CDC-6CA8-5F48-8EC6DA8624CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
+++ b/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\uiri-ims\documentation\srs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259534EA-6937-4B31-9B8D-E5468C435218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A2C8FE-8527-4312-A909-D8A33F447755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4665" yWindow="2985" windowWidth="15375" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSchedule" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="85">
   <si>
     <t>TASK</t>
   </si>
@@ -178,9 +178,6 @@
     <t>Keith &amp; Deo</t>
   </si>
   <si>
-    <t>Security requirements and audit review</t>
-  </si>
-  <si>
     <t>Phase 3: Database Design and Documentation</t>
   </si>
   <si>
@@ -196,9 +193,6 @@
     <t>Logical ERD and 3NF normalization</t>
   </si>
   <si>
-    <t>Extended ERD review and corrections</t>
-  </si>
-  <si>
     <t>Phase 4: Database Implementation</t>
   </si>
   <si>
@@ -208,57 +202,6 @@
     <t>Primary keys, foreign keys and constraints</t>
   </si>
   <si>
-    <t>Campus, department and category seed data</t>
-  </si>
-  <si>
-    <t>Authentication and RBAC tables</t>
-  </si>
-  <si>
-    <t>Database integrity review</t>
-  </si>
-  <si>
-    <t>Phase 5: Application Modules, Testing and Documentation</t>
-  </si>
-  <si>
-    <t>Inventory item and asset instance module</t>
-  </si>
-  <si>
-    <t>Stock in, stock out and transfer module</t>
-  </si>
-  <si>
-    <t>Supplier, dashboard and reports module</t>
-  </si>
-  <si>
-    <t>Security, audit trail and validation checks</t>
-  </si>
-  <si>
-    <t>System testing and correction</t>
-  </si>
-  <si>
-    <t>Phase 6: Presentation and Final Submission</t>
-  </si>
-  <si>
-    <t>Final proposal and SRS packaging</t>
-  </si>
-  <si>
-    <t>ERD and UML diagrams finalization in Visio</t>
-  </si>
-  <si>
-    <t>Deo</t>
-  </si>
-  <si>
-    <t>User manual and final project report</t>
-  </si>
-  <si>
-    <t>Presentation slides and demonstration script</t>
-  </si>
-  <si>
-    <t>Supervisor presentation and handover</t>
-  </si>
-  <si>
-    <t>UIRI Inventory Management System Work Plan</t>
-  </si>
-  <si>
     <t>Project</t>
   </si>
   <si>
@@ -289,21 +232,12 @@
     <t>Keith Paul Kato</t>
   </si>
   <si>
-    <t>Lead reporter, database design, normalization, schema implementation</t>
-  </si>
-  <si>
     <t>Komukama Tracy</t>
   </si>
   <si>
-    <t>Requirements, SRS, documentation, supplier and report module support</t>
-  </si>
-  <si>
     <t>Atuhiire Deo Kamate</t>
   </si>
   <si>
-    <t>Data dictionary, UML diagrams, testing and dashboard support</t>
-  </si>
-  <si>
     <t>Supervisor</t>
   </si>
   <si>
@@ -320,6 +254,75 @@
   </si>
   <si>
     <t>Database Project Team:</t>
+  </si>
+  <si>
+    <t>Phase 5: Application Modules, Security Hardening and Deployment</t>
+  </si>
+  <si>
+    <t>Phase 6: Testing, Documentation and Final Submission</t>
+  </si>
+  <si>
+    <t>Security requirements, session policy and audit review</t>
+  </si>
+  <si>
+    <t>Extended ERD review and implementation corrections</t>
+  </si>
+  <si>
+    <t>Campus, department, category and inventory seed data</t>
+  </si>
+  <si>
+    <t>Tracy &amp; Keith</t>
+  </si>
+  <si>
+    <t>Authentication, RBAC and session security tables</t>
+  </si>
+  <si>
+    <t>Database integrity, audit and deployment readiness review</t>
+  </si>
+  <si>
+    <t>Inventory item registration, details preview and item-print workflow</t>
+  </si>
+  <si>
+    <t>Stock-in, stock-out, adjustment and recent movement panels</t>
+  </si>
+  <si>
+    <t>Supplier, management tables, delete confirmations and UI consistency</t>
+  </si>
+  <si>
+    <t>Dashboard, analytics, reports and table visual standardisation</t>
+  </si>
+  <si>
+    <t>Idle timeout, landing-page logout behaviour and Alwaysdata deployment</t>
+  </si>
+  <si>
+    <t>Evidence screenshots, progress report update and workplan appendix image</t>
+  </si>
+  <si>
+    <t>Final UAT checklist for authentication, inventory, stock, reports and audit trail</t>
+  </si>
+  <si>
+    <t>Deo &amp; Keith</t>
+  </si>
+  <si>
+    <t>User manual and final project report packaging</t>
+  </si>
+  <si>
+    <t>Presentation slides, demonstration script and supervisor review</t>
+  </si>
+  <si>
+    <t>Supervisor presentation, handover and final corrections</t>
+  </si>
+  <si>
+    <t>UIRI Inventory Management System Work Plan - Updated 19 July 2026</t>
+  </si>
+  <si>
+    <t>Lead reporter; database design; PHP/MySQL implementation; security hardening; Alwaysdata deployment coordination.</t>
+  </si>
+  <si>
+    <t>Requirements and SRS review; documentation quality control; user workflow validation and report evidence support.</t>
+  </si>
+  <si>
+    <t>Data dictionary, UML/database validation, test support and final UAT evidence preparation.</t>
   </si>
 </sst>
 </file>
@@ -1432,6 +1435,114 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1BF44AF-1AC0-E7EA-4A5A-3409B64C9809}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EBEA110-3E52-7FC6-102F-6D60E09B97D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9810750"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1642,13 +1753,13 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="32" style="13" customWidth="1"/>
-    <col min="3" max="3" width="18" style="13" customWidth="1"/>
-    <col min="4" max="4" width="10" style="13" customWidth="1"/>
-    <col min="5" max="5" width="10" style="21" customWidth="1"/>
-    <col min="6" max="6" width="10" style="13" customWidth="1"/>
+    <col min="2" max="2" width="48.7109375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="21" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="13" customWidth="1"/>
     <col min="7" max="7" width="2.7109375" style="13" customWidth="1"/>
-    <col min="8" max="8" width="6" style="13" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="13" customWidth="1"/>
     <col min="9" max="50" width="3" customWidth="1"/>
     <col min="51" max="64" width="2.5703125" style="13" customWidth="1"/>
     <col min="65" max="65" width="9.140625" style="13" customWidth="1"/>
@@ -1701,14 +1812,14 @@
     </row>
     <row r="3" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C3"/>
       <c r="D3" s="19" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="129">
-        <v>46201</v>
+        <v>46222</v>
       </c>
       <c r="F3" s="130"/>
     </row>
@@ -1721,7 +1832,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4"/>
       <c r="I4" s="123">
@@ -3086,7 +3197,7 @@
       <c r="BK17" s="42"/>
       <c r="BL17" s="42"/>
     </row>
-    <row r="18" spans="1:64" s="30" customFormat="1" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19"/>
       <c r="B18" s="67" t="s">
         <v>34</v>
@@ -3165,27 +3276,27 @@
       <c r="BK18" s="42"/>
       <c r="BL18" s="42"/>
     </row>
-    <row r="19" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19"/>
       <c r="B19" s="67" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D19" s="110">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="E19" s="63">
         <v>46200</v>
       </c>
       <c r="F19" s="113">
-        <v>46201</v>
+        <v>46222</v>
       </c>
       <c r="G19" s="28"/>
       <c r="H19" s="64">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v>23</v>
       </c>
       <c r="I19" s="42"/>
       <c r="J19" s="42"/>
@@ -3244,10 +3355,10 @@
       <c r="BK19" s="42"/>
       <c r="BL19" s="42"/>
     </row>
-    <row r="20" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19"/>
       <c r="B20" s="70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="71"/>
       <c r="D20" s="106"/>
@@ -3315,10 +3426,10 @@
       <c r="BK20" s="42"/>
       <c r="BL20" s="42"/>
     </row>
-    <row r="21" spans="1:64" s="30" customFormat="1" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19"/>
       <c r="B21" s="76" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="77" t="s">
         <v>26</v>
@@ -3394,10 +3505,10 @@
       <c r="BK21" s="42"/>
       <c r="BL21" s="42"/>
     </row>
-    <row r="22" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19"/>
       <c r="B22" s="76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="77" t="s">
         <v>24</v>
@@ -3473,10 +3584,10 @@
       <c r="BK22" s="42"/>
       <c r="BL22" s="42"/>
     </row>
-    <row r="23" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19"/>
       <c r="B23" s="76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="77" t="s">
         <v>35</v>
@@ -3552,10 +3663,10 @@
       <c r="BK23" s="42"/>
       <c r="BL23" s="42"/>
     </row>
-    <row r="24" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19"/>
       <c r="B24" s="76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="77" t="s">
         <v>26</v>
@@ -3631,16 +3742,16 @@
       <c r="BK24" s="42"/>
       <c r="BL24" s="42"/>
     </row>
-    <row r="25" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19"/>
       <c r="B25" s="76" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C25" s="77" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="110">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" s="72">
         <v>46207</v>
@@ -3650,7 +3761,7 @@
       </c>
       <c r="G25" s="28"/>
       <c r="H25" s="73">
-        <f t="shared" si="6"/>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>2</v>
       </c>
       <c r="I25" s="42"/>
@@ -3710,10 +3821,10 @@
       <c r="BK25" s="42"/>
       <c r="BL25" s="42"/>
     </row>
-    <row r="26" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19"/>
       <c r="B26" s="79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C26" s="80"/>
       <c r="D26" s="107"/>
@@ -3781,10 +3892,10 @@
       <c r="BK26" s="42"/>
       <c r="BL26" s="42"/>
     </row>
-    <row r="27" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19"/>
       <c r="B27" s="85" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" s="86" t="s">
         <v>26</v>
@@ -3860,10 +3971,10 @@
       <c r="BK27" s="42"/>
       <c r="BL27" s="42"/>
     </row>
-    <row r="28" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19"/>
       <c r="B28" s="85" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C28" s="86" t="s">
         <v>35</v>
@@ -3939,27 +4050,27 @@
       <c r="BK28" s="42"/>
       <c r="BL28" s="42"/>
     </row>
-    <row r="29" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19"/>
       <c r="B29" s="85" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C29" s="86" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D29" s="110">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E29" s="81">
         <v>46211</v>
       </c>
       <c r="F29" s="117">
-        <v>46212</v>
+        <v>46222</v>
       </c>
       <c r="G29" s="28"/>
       <c r="H29" s="82">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v>12</v>
       </c>
       <c r="I29" s="42"/>
       <c r="J29" s="42"/>
@@ -4018,27 +4129,27 @@
       <c r="BK29" s="42"/>
       <c r="BL29" s="42"/>
     </row>
-    <row r="30" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19"/>
       <c r="B30" s="85" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C30" s="86" t="s">
         <v>26</v>
       </c>
       <c r="D30" s="110">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="E30" s="81">
         <v>46212</v>
       </c>
       <c r="F30" s="117">
-        <v>46213</v>
+        <v>46222</v>
       </c>
       <c r="G30" s="28"/>
       <c r="H30" s="82">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v>11</v>
       </c>
       <c r="I30" s="42"/>
       <c r="J30" s="42"/>
@@ -4097,27 +4208,27 @@
       <c r="BK30" s="42"/>
       <c r="BL30" s="42"/>
     </row>
-    <row r="31" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19"/>
       <c r="B31" s="85" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C31" s="86" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="110">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E31" s="81">
         <v>46213</v>
       </c>
       <c r="F31" s="117">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="G31" s="28"/>
       <c r="H31" s="82">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v>10</v>
       </c>
       <c r="I31" s="42"/>
       <c r="J31" s="42"/>
@@ -4176,10 +4287,10 @@
       <c r="BK31" s="42"/>
       <c r="BL31" s="42"/>
     </row>
-    <row r="32" spans="1:64" s="30" customFormat="1" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19"/>
       <c r="B32" s="50" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="108"/>
@@ -4247,27 +4358,27 @@
       <c r="BK32" s="42"/>
       <c r="BL32" s="42"/>
     </row>
-    <row r="33" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19"/>
       <c r="B33" s="57" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C33" s="58" t="s">
         <v>22</v>
       </c>
       <c r="D33" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="59">
         <v>46216</v>
       </c>
       <c r="F33" s="111">
-        <v>46218</v>
+        <v>46222</v>
       </c>
       <c r="G33" s="28"/>
       <c r="H33" s="52">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v>7</v>
       </c>
       <c r="I33" s="42"/>
       <c r="J33" s="42"/>
@@ -4326,27 +4437,27 @@
       <c r="BK33" s="42"/>
       <c r="BL33" s="42"/>
     </row>
-    <row r="34" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19"/>
       <c r="B34" s="57" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C34" s="58" t="s">
         <v>35</v>
       </c>
       <c r="D34" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="59">
         <v>46217</v>
       </c>
       <c r="F34" s="111">
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="G34" s="28"/>
       <c r="H34" s="52">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v>6</v>
       </c>
       <c r="I34" s="42"/>
       <c r="J34" s="42"/>
@@ -4405,27 +4516,27 @@
       <c r="BK34" s="42"/>
       <c r="BL34" s="42"/>
     </row>
-    <row r="35" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:64" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19"/>
       <c r="B35" s="57" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C35" s="58" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D35" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="59">
         <v>46218</v>
       </c>
       <c r="F35" s="111">
-        <v>46220</v>
+        <v>46222</v>
       </c>
       <c r="G35" s="28"/>
       <c r="H35" s="52">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v>5</v>
       </c>
       <c r="I35" s="42"/>
       <c r="J35" s="42"/>
@@ -4484,27 +4595,27 @@
       <c r="BK35" s="42"/>
       <c r="BL35" s="42"/>
     </row>
-    <row r="36" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19"/>
       <c r="B36" s="57" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C36" s="58" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D36" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="59">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="F36" s="111">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="G36" s="28"/>
       <c r="H36" s="52">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v>4</v>
       </c>
       <c r="I36" s="42"/>
       <c r="J36" s="42"/>
@@ -4563,26 +4674,27 @@
       <c r="BK36" s="42"/>
       <c r="BL36" s="42"/>
     </row>
-    <row r="37" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:64" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19"/>
       <c r="B37" s="57" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C37" s="58" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D37" s="110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="59">
-        <v>46221</v>
+        <v>46220</v>
       </c>
       <c r="F37" s="111">
         <v>46222</v>
       </c>
       <c r="G37" s="28"/>
       <c r="H37" s="52">
-        <v>2</v>
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <v>3</v>
       </c>
       <c r="I37" s="42"/>
       <c r="J37" s="42"/>
@@ -4641,10 +4753,10 @@
       <c r="BK37" s="42"/>
       <c r="BL37" s="42"/>
     </row>
-    <row r="38" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19"/>
       <c r="B38" s="90" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C38" s="94"/>
       <c r="D38" s="109"/>
@@ -4709,25 +4821,26 @@
       <c r="BK38" s="42"/>
       <c r="BL38" s="42"/>
     </row>
-    <row r="39" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:64" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19"/>
       <c r="B39" s="97" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C39" s="91" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D39" s="110">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E39" s="92">
+        <v>46222</v>
+      </c>
+      <c r="F39" s="120">
         <v>46223</v>
-      </c>
-      <c r="F39" s="120">
-        <v>46224</v>
       </c>
       <c r="G39" s="28"/>
       <c r="H39" s="93">
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>2</v>
       </c>
       <c r="I39" s="42"/>
@@ -4787,16 +4900,16 @@
       <c r="BK39" s="42"/>
       <c r="BL39" s="42"/>
     </row>
-    <row r="40" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:64" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19"/>
       <c r="B40" s="99" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C40" s="91" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D40" s="110">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="E40" s="92">
         <v>46223</v>
@@ -4806,6 +4919,7 @@
       </c>
       <c r="G40" s="28"/>
       <c r="H40" s="93">
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>3</v>
       </c>
       <c r="I40" s="42"/>
@@ -4865,16 +4979,16 @@
       <c r="BK40" s="42"/>
       <c r="BL40" s="42"/>
     </row>
-    <row r="41" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19"/>
       <c r="B41" s="97" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C41" s="91" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="110">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="E41" s="92">
         <v>46224</v>
@@ -4884,6 +4998,7 @@
       </c>
       <c r="G41" s="28"/>
       <c r="H41" s="93">
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>3</v>
       </c>
       <c r="I41" s="42"/>
@@ -4943,16 +5058,16 @@
       <c r="BK41" s="42"/>
       <c r="BL41" s="42"/>
     </row>
-    <row r="42" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19"/>
       <c r="B42" s="97" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C42" s="91" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="110">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E42" s="92">
         <v>46225</v>
@@ -4962,6 +5077,7 @@
       </c>
       <c r="G42" s="28"/>
       <c r="H42" s="93">
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>3</v>
       </c>
       <c r="I42" s="42"/>
@@ -5021,16 +5137,16 @@
       <c r="BK42" s="42"/>
       <c r="BL42" s="42"/>
     </row>
-    <row r="43" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19"/>
       <c r="B43" s="97" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C43" s="91" t="s">
         <v>20</v>
       </c>
       <c r="D43" s="110">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E43" s="92">
         <v>46227</v>
@@ -5040,6 +5156,7 @@
       </c>
       <c r="G43" s="28"/>
       <c r="H43" s="93">
+        <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>1</v>
       </c>
       <c r="I43" s="42"/>
@@ -5099,7 +5216,7 @@
       <c r="BK43" s="42"/>
       <c r="BL43" s="42"/>
     </row>
-    <row r="44" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19"/>
       <c r="B44" s="40"/>
       <c r="C44" s="39"/>
@@ -5557,31 +5674,31 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B1"/>
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B4" s="104">
         <v>46188</v>
@@ -5589,63 +5706,63 @@
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="7" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="7" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>13</v>

--- a/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
+++ b/documentation/srs/UIRI_IMS_Updated_Workplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\uiri-ims\documentation\srs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A2C8FE-8527-4312-A909-D8A33F447755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75AD659-99E2-45E7-AAC3-18ABE7F3B6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4665" yWindow="2985" windowWidth="15375" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSchedule" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
     <numFmt numFmtId="167" formatCode="d"/>
     <numFmt numFmtId="168" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,11 +354,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="0"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -574,7 +569,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -711,6 +706,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -719,32 +727,32 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -753,358 +761,322 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="23" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="23" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="23" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="17" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="17" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1543,6 +1515,114 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80280242-ADBC-B2BF-61FE-A70A716D4B7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11877675" cy="9915525"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82C3975A-1756-DA8C-59CA-F836B8219402}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11877675" cy="10067925"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1749,26 +1829,25 @@
   <sheetPr>
     <tabColor theme="2" tint="-0.49995422223578601"/>
   </sheetPr>
-  <dimension ref="A1:BL49"/>
+  <dimension ref="A1:AX49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="48.7109375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" style="13" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="21" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="13" customWidth="1"/>
+    <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.7109375" style="13" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" style="13" customWidth="1"/>
+    <col min="8" max="8" width="4.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="50" width="3" customWidth="1"/>
-    <col min="51" max="64" width="2.5703125" style="13" customWidth="1"/>
-    <col min="65" max="65" width="9.140625" style="13" customWidth="1"/>
-    <col min="66" max="68" width="9.140625" style="13"/>
-    <col min="69" max="70" width="10.28515625" style="13"/>
-    <col min="71" max="16384" width="9.140625" style="13"/>
+    <col min="51" max="51" width="9.140625" style="13" customWidth="1"/>
+    <col min="52" max="54" width="9.140625" style="13"/>
+    <col min="55" max="56" width="10.28515625" style="13"/>
+    <col min="57" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="B1" s="38" t="s">
         <v>12</v>
       </c>
@@ -1779,7 +1858,7 @@
       <c r="H1" s="15"/>
       <c r="I1" s="18"/>
     </row>
-    <row r="2" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="13" t="s">
         <v>13</v>
       </c>
@@ -1787,30 +1866,30 @@
       <c r="D2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="129">
+      <c r="E2" s="113">
         <v>46188</v>
       </c>
-      <c r="F2" s="130"/>
-      <c r="T2" s="131"/>
-      <c r="U2" s="131"/>
-      <c r="V2" s="131"/>
-      <c r="W2" s="131"/>
-      <c r="X2" s="131"/>
-      <c r="Y2" s="131"/>
-      <c r="Z2" s="131"/>
-      <c r="AA2" s="131"/>
-      <c r="AB2" s="131"/>
-      <c r="AC2" s="131"/>
-      <c r="AD2" s="131"/>
-      <c r="AE2" s="131"/>
-      <c r="AF2" s="131"/>
-      <c r="AG2" s="131"/>
-      <c r="AH2" s="131"/>
-      <c r="AI2" s="131"/>
-      <c r="AJ2" s="131"/>
-      <c r="AK2" s="131"/>
-    </row>
-    <row r="3" spans="1:64" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="114"/>
+      <c r="T2" s="115"/>
+      <c r="U2" s="115"/>
+      <c r="V2" s="115"/>
+      <c r="W2" s="115"/>
+      <c r="X2" s="115"/>
+      <c r="Y2" s="115"/>
+      <c r="Z2" s="115"/>
+      <c r="AA2" s="115"/>
+      <c r="AB2" s="115"/>
+      <c r="AC2" s="115"/>
+      <c r="AD2" s="115"/>
+      <c r="AE2" s="115"/>
+      <c r="AF2" s="115"/>
+      <c r="AG2" s="115"/>
+      <c r="AH2" s="115"/>
+      <c r="AI2" s="115"/>
+      <c r="AJ2" s="115"/>
+      <c r="AK2" s="115"/>
+    </row>
+    <row r="3" spans="1:50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>61</v>
       </c>
@@ -1818,12 +1897,12 @@
       <c r="D3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="129">
+      <c r="E3" s="113">
         <v>46222</v>
       </c>
-      <c r="F3" s="130"/>
-    </row>
-    <row r="4" spans="1:64" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="114"/>
+    </row>
+    <row r="4" spans="1:50" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>16</v>
       </c>
@@ -1835,76 +1914,62 @@
         <v>5</v>
       </c>
       <c r="F4"/>
-      <c r="I4" s="123">
+      <c r="I4" s="110">
         <v>46188</v>
       </c>
-      <c r="J4" s="124"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="124"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="125"/>
-      <c r="P4" s="123">
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="110">
         <v>46195</v>
       </c>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="124"/>
-      <c r="S4" s="124"/>
-      <c r="T4" s="124"/>
-      <c r="U4" s="124"/>
-      <c r="V4" s="125"/>
-      <c r="W4" s="123">
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="110">
         <v>46202</v>
       </c>
-      <c r="X4" s="124"/>
-      <c r="Y4" s="124"/>
-      <c r="Z4" s="124"/>
-      <c r="AA4" s="124"/>
-      <c r="AB4" s="124"/>
-      <c r="AC4" s="125"/>
-      <c r="AD4" s="123">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="111"/>
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="110">
         <v>46209</v>
       </c>
-      <c r="AE4" s="124"/>
-      <c r="AF4" s="124"/>
-      <c r="AG4" s="124"/>
-      <c r="AH4" s="124"/>
-      <c r="AI4" s="124"/>
-      <c r="AJ4" s="125"/>
-      <c r="AK4" s="123">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="110">
         <v>46216</v>
       </c>
-      <c r="AL4" s="124"/>
-      <c r="AM4" s="124"/>
-      <c r="AN4" s="124"/>
-      <c r="AO4" s="124"/>
-      <c r="AP4" s="124"/>
-      <c r="AQ4" s="125"/>
-      <c r="AR4" s="123">
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="111"/>
+      <c r="AQ4" s="112"/>
+      <c r="AR4" s="110">
         <v>46223</v>
       </c>
-      <c r="AS4" s="124"/>
-      <c r="AT4" s="124"/>
-      <c r="AU4" s="124"/>
-      <c r="AV4" s="124"/>
-      <c r="AW4" s="124"/>
-      <c r="AX4" s="125"/>
-      <c r="AY4" s="126"/>
-      <c r="AZ4" s="127"/>
-      <c r="BA4" s="127"/>
-      <c r="BB4" s="127"/>
-      <c r="BC4" s="127"/>
-      <c r="BD4" s="127"/>
-      <c r="BE4" s="128"/>
-      <c r="BF4" s="126"/>
-      <c r="BG4" s="127"/>
-      <c r="BH4" s="127"/>
-      <c r="BI4" s="127"/>
-      <c r="BJ4" s="127"/>
-      <c r="BK4" s="127"/>
-      <c r="BL4" s="128"/>
-    </row>
-    <row r="5" spans="1:64" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="AS4" s="111"/>
+      <c r="AT4" s="111"/>
+      <c r="AU4" s="111"/>
+      <c r="AV4" s="111"/>
+      <c r="AW4" s="111"/>
+      <c r="AX4" s="112"/>
+    </row>
+    <row r="5" spans="1:50" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A5" s="19"/>
       <c r="G5" s="19"/>
       <c r="I5" s="47">
@@ -2063,52 +2128,8 @@
         <f t="shared" si="0"/>
         <v>46229</v>
       </c>
-      <c r="AY5" s="100"/>
-      <c r="AZ5" s="101"/>
-      <c r="BA5" s="101">
-        <f t="shared" ref="BA5:BE5" si="1">AZ5+1</f>
-        <v>1</v>
-      </c>
-      <c r="BB5" s="101">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="BC5" s="101">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="BD5" s="101">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="BE5" s="102">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="BF5" s="100"/>
-      <c r="BG5" s="101"/>
-      <c r="BH5" s="101">
-        <f t="shared" ref="BH5:BL5" si="2">BG5+1</f>
-        <v>1</v>
-      </c>
-      <c r="BI5" s="101">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="BJ5" s="101">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="BK5" s="101">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="BL5" s="102">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:64" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:50" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
       <c r="B6" s="44" t="s">
         <v>0</v>
@@ -2130,231 +2151,175 @@
         <v>5</v>
       </c>
       <c r="I6" s="46" t="str">
-        <f t="shared" ref="I6" si="3">LEFT(TEXT(I5,"ddd"),1)</f>
+        <f t="shared" ref="I6" si="1">LEFT(TEXT(I5,"ddd"),1)</f>
         <v>M</v>
       </c>
       <c r="J6" s="46" t="str">
-        <f t="shared" ref="J6:AR6" si="4">LEFT(TEXT(J5,"ddd"),1)</f>
+        <f t="shared" ref="J6:AR6" si="2">LEFT(TEXT(J5,"ddd"),1)</f>
         <v>T</v>
       </c>
       <c r="K6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>W</v>
       </c>
       <c r="L6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="M6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>F</v>
       </c>
       <c r="N6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="O6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="P6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="Q6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="R6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>W</v>
       </c>
       <c r="S6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="T6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>F</v>
       </c>
       <c r="U6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="V6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="W6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="X6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="Y6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>W</v>
       </c>
       <c r="Z6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="AA6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>F</v>
       </c>
       <c r="AB6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AC6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AD6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AE6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="AF6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>W</v>
       </c>
       <c r="AG6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="AH6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>F</v>
       </c>
       <c r="AI6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AJ6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AK6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AL6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="AM6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>W</v>
       </c>
       <c r="AN6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>T</v>
       </c>
       <c r="AO6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>F</v>
       </c>
       <c r="AP6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AQ6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>S</v>
       </c>
       <c r="AR6" s="46" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="AS6" s="46" t="str">
-        <f t="shared" ref="AS6:BL6" si="5">LEFT(TEXT(AS5,"ddd"),1)</f>
+        <f t="shared" ref="AS6:AX6" si="3">LEFT(TEXT(AS5,"ddd"),1)</f>
         <v>T</v>
       </c>
       <c r="AT6" s="46" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>W</v>
       </c>
       <c r="AU6" s="46" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="AV6" s="46" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="AW6" s="46" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AX6" s="46" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="AY6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>S</v>
-      </c>
-      <c r="AZ6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>S</v>
-      </c>
-      <c r="BA6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>S</v>
-      </c>
-      <c r="BB6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
-      </c>
-      <c r="BC6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>T</v>
-      </c>
-      <c r="BD6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>W</v>
-      </c>
-      <c r="BE6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>T</v>
-      </c>
-      <c r="BF6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>S</v>
-      </c>
-      <c r="BG6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>S</v>
-      </c>
-      <c r="BH6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>S</v>
-      </c>
-      <c r="BI6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>M</v>
-      </c>
-      <c r="BJ6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>T</v>
-      </c>
-      <c r="BK6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>W</v>
-      </c>
-      <c r="BL6" s="103" t="str">
-        <f t="shared" si="5"/>
-        <v>T</v>
-      </c>
-    </row>
-    <row r="7" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
@@ -2363,7 +2328,7 @@
       <c r="F7" s="27"/>
       <c r="G7" s="28"/>
       <c r="H7" s="28" t="str">
-        <f t="shared" ref="H7:H48" si="6">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H7:H48" si="4">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I7" s="29"/>
@@ -2408,22 +2373,8 @@
       <c r="AV7" s="29"/>
       <c r="AW7" s="29"/>
       <c r="AX7" s="29"/>
-      <c r="AY7" s="42"/>
-      <c r="AZ7" s="42"/>
-      <c r="BA7" s="42"/>
-      <c r="BB7" s="42"/>
-      <c r="BC7" s="42"/>
-      <c r="BD7" s="42"/>
-      <c r="BE7" s="42"/>
-      <c r="BF7" s="42"/>
-      <c r="BG7" s="42"/>
-      <c r="BH7" s="42"/>
-      <c r="BI7" s="42"/>
-      <c r="BJ7" s="42"/>
-      <c r="BK7" s="42"/>
-      <c r="BL7" s="42"/>
-    </row>
-    <row r="8" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
       <c r="B8" s="50" t="s">
         <v>18</v>
@@ -2434,7 +2385,7 @@
       <c r="F8" s="55"/>
       <c r="G8" s="56"/>
       <c r="H8" s="56" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I8" s="42"/>
@@ -2479,22 +2430,8 @@
       <c r="AV8" s="42"/>
       <c r="AW8" s="42"/>
       <c r="AX8" s="42"/>
-      <c r="AY8" s="42"/>
-      <c r="AZ8" s="42"/>
-      <c r="BA8" s="42"/>
-      <c r="BB8" s="42"/>
-      <c r="BC8" s="42"/>
-      <c r="BD8" s="42"/>
-      <c r="BE8" s="42"/>
-      <c r="BF8" s="42"/>
-      <c r="BG8" s="42"/>
-      <c r="BH8" s="42"/>
-      <c r="BI8" s="42"/>
-      <c r="BJ8" s="42"/>
-      <c r="BK8" s="42"/>
-      <c r="BL8" s="42"/>
-    </row>
-    <row r="9" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
       <c r="B9" s="57" t="s">
         <v>19</v>
@@ -2502,18 +2439,18 @@
       <c r="C9" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="110">
+      <c r="D9" s="99">
         <v>1</v>
       </c>
       <c r="E9" s="59">
         <v>46188</v>
       </c>
-      <c r="F9" s="111">
+      <c r="F9" s="100">
         <v>46188</v>
       </c>
       <c r="G9" s="28"/>
       <c r="H9" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I9" s="60"/>
@@ -2558,22 +2495,8 @@
       <c r="AV9" s="42"/>
       <c r="AW9" s="42"/>
       <c r="AX9" s="42"/>
-      <c r="AY9" s="42"/>
-      <c r="AZ9" s="42"/>
-      <c r="BA9" s="42"/>
-      <c r="BB9" s="42"/>
-      <c r="BC9" s="42"/>
-      <c r="BD9" s="42"/>
-      <c r="BE9" s="42"/>
-      <c r="BF9" s="42"/>
-      <c r="BG9" s="42"/>
-      <c r="BH9" s="42"/>
-      <c r="BI9" s="42"/>
-      <c r="BJ9" s="42"/>
-      <c r="BK9" s="42"/>
-      <c r="BL9" s="42"/>
-    </row>
-    <row r="10" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
       <c r="B10" s="57" t="s">
         <v>21</v>
@@ -2581,18 +2504,18 @@
       <c r="C10" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="110">
+      <c r="D10" s="99">
         <v>1</v>
       </c>
       <c r="E10" s="59">
         <v>46188</v>
       </c>
-      <c r="F10" s="111">
+      <c r="F10" s="100">
         <v>46190</v>
       </c>
       <c r="G10" s="28"/>
       <c r="H10" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="I10" s="60"/>
@@ -2637,22 +2560,8 @@
       <c r="AV10" s="42"/>
       <c r="AW10" s="42"/>
       <c r="AX10" s="42"/>
-      <c r="AY10" s="42"/>
-      <c r="AZ10" s="42"/>
-      <c r="BA10" s="42"/>
-      <c r="BB10" s="42"/>
-      <c r="BC10" s="42"/>
-      <c r="BD10" s="42"/>
-      <c r="BE10" s="42"/>
-      <c r="BF10" s="42"/>
-      <c r="BG10" s="42"/>
-      <c r="BH10" s="42"/>
-      <c r="BI10" s="42"/>
-      <c r="BJ10" s="42"/>
-      <c r="BK10" s="42"/>
-      <c r="BL10" s="42"/>
-    </row>
-    <row r="11" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19"/>
       <c r="B11" s="57" t="s">
         <v>23</v>
@@ -2660,18 +2569,18 @@
       <c r="C11" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="110">
+      <c r="D11" s="99">
         <v>1</v>
       </c>
       <c r="E11" s="59">
         <v>46189</v>
       </c>
-      <c r="F11" s="111">
+      <c r="F11" s="100">
         <v>46192</v>
       </c>
       <c r="G11" s="28"/>
       <c r="H11" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="I11" s="42"/>
@@ -2716,22 +2625,8 @@
       <c r="AV11" s="42"/>
       <c r="AW11" s="42"/>
       <c r="AX11" s="42"/>
-      <c r="AY11" s="42"/>
-      <c r="AZ11" s="42"/>
-      <c r="BA11" s="42"/>
-      <c r="BB11" s="42"/>
-      <c r="BC11" s="42"/>
-      <c r="BD11" s="42"/>
-      <c r="BE11" s="42"/>
-      <c r="BF11" s="42"/>
-      <c r="BG11" s="42"/>
-      <c r="BH11" s="42"/>
-      <c r="BI11" s="42"/>
-      <c r="BJ11" s="42"/>
-      <c r="BK11" s="42"/>
-      <c r="BL11" s="42"/>
-    </row>
-    <row r="12" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="B12" s="57" t="s">
         <v>25</v>
@@ -2739,18 +2634,18 @@
       <c r="C12" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="110">
+      <c r="D12" s="99">
         <v>1</v>
       </c>
       <c r="E12" s="59">
         <v>46190</v>
       </c>
-      <c r="F12" s="111">
+      <c r="F12" s="100">
         <v>46192</v>
       </c>
       <c r="G12" s="28"/>
       <c r="H12" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="I12" s="42"/>
@@ -2795,22 +2690,8 @@
       <c r="AV12" s="42"/>
       <c r="AW12" s="42"/>
       <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
-      <c r="BB12" s="42"/>
-      <c r="BC12" s="42"/>
-      <c r="BD12" s="42"/>
-      <c r="BE12" s="42"/>
-      <c r="BF12" s="42"/>
-      <c r="BG12" s="42"/>
-      <c r="BH12" s="42"/>
-      <c r="BI12" s="42"/>
-      <c r="BJ12" s="42"/>
-      <c r="BK12" s="42"/>
-      <c r="BL12" s="42"/>
-    </row>
-    <row r="13" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19"/>
       <c r="B13" s="57" t="s">
         <v>27</v>
@@ -2818,18 +2699,18 @@
       <c r="C13" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="110">
+      <c r="D13" s="99">
         <v>1</v>
       </c>
       <c r="E13" s="59">
         <v>46191</v>
       </c>
-      <c r="F13" s="111">
+      <c r="F13" s="100">
         <v>46194</v>
       </c>
       <c r="G13" s="28"/>
       <c r="H13" s="52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="I13" s="42"/>
@@ -2874,33 +2755,19 @@
       <c r="AV13" s="42"/>
       <c r="AW13" s="42"/>
       <c r="AX13" s="42"/>
-      <c r="AY13" s="42"/>
-      <c r="AZ13" s="42"/>
-      <c r="BA13" s="42"/>
-      <c r="BB13" s="42"/>
-      <c r="BC13" s="42"/>
-      <c r="BD13" s="42"/>
-      <c r="BE13" s="42"/>
-      <c r="BF13" s="42"/>
-      <c r="BG13" s="42"/>
-      <c r="BH13" s="42"/>
-      <c r="BI13" s="42"/>
-      <c r="BJ13" s="42"/>
-      <c r="BK13" s="42"/>
-      <c r="BL13" s="42"/>
-    </row>
-    <row r="14" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19"/>
       <c r="B14" s="61" t="s">
         <v>28</v>
       </c>
       <c r="C14" s="62"/>
-      <c r="D14" s="105"/>
+      <c r="D14" s="96"/>
       <c r="E14" s="65"/>
-      <c r="F14" s="112"/>
+      <c r="F14" s="101"/>
       <c r="G14" s="66"/>
       <c r="H14" s="66" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I14" s="42"/>
@@ -2945,22 +2812,8 @@
       <c r="AV14" s="42"/>
       <c r="AW14" s="42"/>
       <c r="AX14" s="42"/>
-      <c r="AY14" s="42"/>
-      <c r="AZ14" s="42"/>
-      <c r="BA14" s="42"/>
-      <c r="BB14" s="42"/>
-      <c r="BC14" s="42"/>
-      <c r="BD14" s="42"/>
-      <c r="BE14" s="42"/>
-      <c r="BF14" s="42"/>
-      <c r="BG14" s="42"/>
-      <c r="BH14" s="42"/>
-      <c r="BI14" s="42"/>
-      <c r="BJ14" s="42"/>
-      <c r="BK14" s="42"/>
-      <c r="BL14" s="42"/>
-    </row>
-    <row r="15" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19"/>
       <c r="B15" s="67" t="s">
         <v>29</v>
@@ -2968,18 +2821,18 @@
       <c r="C15" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="110">
+      <c r="D15" s="99">
         <v>1</v>
       </c>
       <c r="E15" s="63">
         <v>46195</v>
       </c>
-      <c r="F15" s="113">
+      <c r="F15" s="102">
         <v>46196</v>
       </c>
       <c r="G15" s="28"/>
       <c r="H15" s="64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="I15" s="42"/>
@@ -3024,22 +2877,8 @@
       <c r="AV15" s="42"/>
       <c r="AW15" s="42"/>
       <c r="AX15" s="42"/>
-      <c r="AY15" s="42"/>
-      <c r="AZ15" s="42"/>
-      <c r="BA15" s="42"/>
-      <c r="BB15" s="42"/>
-      <c r="BC15" s="42"/>
-      <c r="BD15" s="42"/>
-      <c r="BE15" s="42"/>
-      <c r="BF15" s="42"/>
-      <c r="BG15" s="42"/>
-      <c r="BH15" s="42"/>
-      <c r="BI15" s="42"/>
-      <c r="BJ15" s="42"/>
-      <c r="BK15" s="42"/>
-      <c r="BL15" s="42"/>
-    </row>
-    <row r="16" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19"/>
       <c r="B16" s="67" t="s">
         <v>30</v>
@@ -3047,18 +2886,18 @@
       <c r="C16" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="110">
+      <c r="D16" s="99">
         <v>1</v>
       </c>
       <c r="E16" s="63">
         <v>46195</v>
       </c>
-      <c r="F16" s="113">
+      <c r="F16" s="102">
         <v>46199</v>
       </c>
       <c r="G16" s="28"/>
       <c r="H16" s="64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="I16" s="42"/>
@@ -3103,22 +2942,8 @@
       <c r="AV16" s="42"/>
       <c r="AW16" s="42"/>
       <c r="AX16" s="42"/>
-      <c r="AY16" s="42"/>
-      <c r="AZ16" s="42"/>
-      <c r="BA16" s="42"/>
-      <c r="BB16" s="42"/>
-      <c r="BC16" s="42"/>
-      <c r="BD16" s="42"/>
-      <c r="BE16" s="42"/>
-      <c r="BF16" s="42"/>
-      <c r="BG16" s="42"/>
-      <c r="BH16" s="42"/>
-      <c r="BI16" s="42"/>
-      <c r="BJ16" s="42"/>
-      <c r="BK16" s="42"/>
-      <c r="BL16" s="42"/>
-    </row>
-    <row r="17" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19"/>
       <c r="B17" s="67" t="s">
         <v>32</v>
@@ -3126,18 +2951,18 @@
       <c r="C17" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="110">
+      <c r="D17" s="99">
         <v>1</v>
       </c>
       <c r="E17" s="63">
         <v>46197</v>
       </c>
-      <c r="F17" s="113">
+      <c r="F17" s="102">
         <v>46200</v>
       </c>
       <c r="G17" s="28"/>
       <c r="H17" s="64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="I17" s="42"/>
@@ -3182,22 +3007,8 @@
       <c r="AV17" s="42"/>
       <c r="AW17" s="42"/>
       <c r="AX17" s="42"/>
-      <c r="AY17" s="42"/>
-      <c r="AZ17" s="42"/>
-      <c r="BA17" s="42"/>
-      <c r="BB17" s="42"/>
-      <c r="BC17" s="42"/>
-      <c r="BD17" s="42"/>
-      <c r="BE17" s="42"/>
-      <c r="BF17" s="42"/>
-      <c r="BG17" s="42"/>
-      <c r="BH17" s="42"/>
-      <c r="BI17" s="42"/>
-      <c r="BJ17" s="42"/>
-      <c r="BK17" s="42"/>
-      <c r="BL17" s="42"/>
-    </row>
-    <row r="18" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19"/>
       <c r="B18" s="67" t="s">
         <v>34</v>
@@ -3205,18 +3016,18 @@
       <c r="C18" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="110">
+      <c r="D18" s="99">
         <v>1</v>
       </c>
       <c r="E18" s="63">
         <v>46196</v>
       </c>
-      <c r="F18" s="113">
+      <c r="F18" s="102">
         <v>46200</v>
       </c>
       <c r="G18" s="28"/>
       <c r="H18" s="64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="I18" s="42"/>
@@ -3261,22 +3072,8 @@
       <c r="AV18" s="42"/>
       <c r="AW18" s="42"/>
       <c r="AX18" s="42"/>
-      <c r="AY18" s="42"/>
-      <c r="AZ18" s="42"/>
-      <c r="BA18" s="42"/>
-      <c r="BB18" s="42"/>
-      <c r="BC18" s="42"/>
-      <c r="BD18" s="42"/>
-      <c r="BE18" s="42"/>
-      <c r="BF18" s="42"/>
-      <c r="BG18" s="42"/>
-      <c r="BH18" s="42"/>
-      <c r="BI18" s="42"/>
-      <c r="BJ18" s="42"/>
-      <c r="BK18" s="42"/>
-      <c r="BL18" s="42"/>
-    </row>
-    <row r="19" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19"/>
       <c r="B19" s="67" t="s">
         <v>64</v>
@@ -3284,13 +3081,13 @@
       <c r="C19" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="110">
+      <c r="D19" s="99">
         <v>1</v>
       </c>
       <c r="E19" s="63">
         <v>46200</v>
       </c>
-      <c r="F19" s="113">
+      <c r="F19" s="102">
         <v>46222</v>
       </c>
       <c r="G19" s="28"/>
@@ -3340,33 +3137,19 @@
       <c r="AV19" s="42"/>
       <c r="AW19" s="42"/>
       <c r="AX19" s="42"/>
-      <c r="AY19" s="42"/>
-      <c r="AZ19" s="42"/>
-      <c r="BA19" s="42"/>
-      <c r="BB19" s="42"/>
-      <c r="BC19" s="42"/>
-      <c r="BD19" s="42"/>
-      <c r="BE19" s="42"/>
-      <c r="BF19" s="42"/>
-      <c r="BG19" s="42"/>
-      <c r="BH19" s="42"/>
-      <c r="BI19" s="42"/>
-      <c r="BJ19" s="42"/>
-      <c r="BK19" s="42"/>
-      <c r="BL19" s="42"/>
-    </row>
-    <row r="20" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19"/>
       <c r="B20" s="70" t="s">
         <v>36</v>
       </c>
       <c r="C20" s="71"/>
-      <c r="D20" s="106"/>
+      <c r="D20" s="97"/>
       <c r="E20" s="74"/>
-      <c r="F20" s="114"/>
+      <c r="F20" s="103"/>
       <c r="G20" s="75"/>
       <c r="H20" s="75" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I20" s="42"/>
@@ -3411,22 +3194,8 @@
       <c r="AV20" s="42"/>
       <c r="AW20" s="42"/>
       <c r="AX20" s="42"/>
-      <c r="AY20" s="42"/>
-      <c r="AZ20" s="42"/>
-      <c r="BA20" s="42"/>
-      <c r="BB20" s="42"/>
-      <c r="BC20" s="42"/>
-      <c r="BD20" s="42"/>
-      <c r="BE20" s="42"/>
-      <c r="BF20" s="42"/>
-      <c r="BG20" s="42"/>
-      <c r="BH20" s="42"/>
-      <c r="BI20" s="42"/>
-      <c r="BJ20" s="42"/>
-      <c r="BK20" s="42"/>
-      <c r="BL20" s="42"/>
-    </row>
-    <row r="21" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19"/>
       <c r="B21" s="76" t="s">
         <v>37</v>
@@ -3434,18 +3203,18 @@
       <c r="C21" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="110">
+      <c r="D21" s="99">
         <v>1</v>
       </c>
       <c r="E21" s="72">
         <v>46202</v>
       </c>
-      <c r="F21" s="115">
+      <c r="F21" s="104">
         <v>46203</v>
       </c>
       <c r="G21" s="28"/>
       <c r="H21" s="73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="I21" s="42"/>
@@ -3490,22 +3259,8 @@
       <c r="AV21" s="42"/>
       <c r="AW21" s="42"/>
       <c r="AX21" s="42"/>
-      <c r="AY21" s="42"/>
-      <c r="AZ21" s="42"/>
-      <c r="BA21" s="42"/>
-      <c r="BB21" s="42"/>
-      <c r="BC21" s="42"/>
-      <c r="BD21" s="42"/>
-      <c r="BE21" s="42"/>
-      <c r="BF21" s="42"/>
-      <c r="BG21" s="42"/>
-      <c r="BH21" s="42"/>
-      <c r="BI21" s="42"/>
-      <c r="BJ21" s="42"/>
-      <c r="BK21" s="42"/>
-      <c r="BL21" s="42"/>
-    </row>
-    <row r="22" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19"/>
       <c r="B22" s="76" t="s">
         <v>38</v>
@@ -3513,18 +3268,18 @@
       <c r="C22" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="110">
+      <c r="D22" s="99">
         <v>1</v>
       </c>
       <c r="E22" s="72">
         <v>46203</v>
       </c>
-      <c r="F22" s="115">
+      <c r="F22" s="104">
         <v>46205</v>
       </c>
       <c r="G22" s="28"/>
       <c r="H22" s="73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="I22" s="42"/>
@@ -3569,22 +3324,8 @@
       <c r="AV22" s="42"/>
       <c r="AW22" s="42"/>
       <c r="AX22" s="42"/>
-      <c r="AY22" s="42"/>
-      <c r="AZ22" s="42"/>
-      <c r="BA22" s="42"/>
-      <c r="BB22" s="42"/>
-      <c r="BC22" s="42"/>
-      <c r="BD22" s="42"/>
-      <c r="BE22" s="42"/>
-      <c r="BF22" s="42"/>
-      <c r="BG22" s="42"/>
-      <c r="BH22" s="42"/>
-      <c r="BI22" s="42"/>
-      <c r="BJ22" s="42"/>
-      <c r="BK22" s="42"/>
-      <c r="BL22" s="42"/>
-    </row>
-    <row r="23" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19"/>
       <c r="B23" s="76" t="s">
         <v>39</v>
@@ -3592,18 +3333,18 @@
       <c r="C23" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="110">
+      <c r="D23" s="99">
         <v>1</v>
       </c>
       <c r="E23" s="72">
         <v>46203</v>
       </c>
-      <c r="F23" s="115">
+      <c r="F23" s="104">
         <v>46206</v>
       </c>
       <c r="G23" s="28"/>
       <c r="H23" s="73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="I23" s="42"/>
@@ -3648,22 +3389,8 @@
       <c r="AV23" s="42"/>
       <c r="AW23" s="42"/>
       <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
-      <c r="BB23" s="42"/>
-      <c r="BC23" s="42"/>
-      <c r="BD23" s="42"/>
-      <c r="BE23" s="42"/>
-      <c r="BF23" s="42"/>
-      <c r="BG23" s="42"/>
-      <c r="BH23" s="42"/>
-      <c r="BI23" s="42"/>
-      <c r="BJ23" s="42"/>
-      <c r="BK23" s="42"/>
-      <c r="BL23" s="42"/>
-    </row>
-    <row r="24" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19"/>
       <c r="B24" s="76" t="s">
         <v>40</v>
@@ -3671,18 +3398,18 @@
       <c r="C24" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="110">
+      <c r="D24" s="99">
         <v>1</v>
       </c>
       <c r="E24" s="72">
         <v>46205</v>
       </c>
-      <c r="F24" s="115">
+      <c r="F24" s="104">
         <v>46207</v>
       </c>
       <c r="G24" s="28"/>
       <c r="H24" s="73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="I24" s="42"/>
@@ -3727,22 +3454,8 @@
       <c r="AV24" s="42"/>
       <c r="AW24" s="42"/>
       <c r="AX24" s="42"/>
-      <c r="AY24" s="42"/>
-      <c r="AZ24" s="42"/>
-      <c r="BA24" s="42"/>
-      <c r="BB24" s="42"/>
-      <c r="BC24" s="42"/>
-      <c r="BD24" s="42"/>
-      <c r="BE24" s="42"/>
-      <c r="BF24" s="42"/>
-      <c r="BG24" s="42"/>
-      <c r="BH24" s="42"/>
-      <c r="BI24" s="42"/>
-      <c r="BJ24" s="42"/>
-      <c r="BK24" s="42"/>
-      <c r="BL24" s="42"/>
-    </row>
-    <row r="25" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19"/>
       <c r="B25" s="76" t="s">
         <v>65</v>
@@ -3750,13 +3463,13 @@
       <c r="C25" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="110">
+      <c r="D25" s="99">
         <v>1</v>
       </c>
       <c r="E25" s="72">
         <v>46207</v>
       </c>
-      <c r="F25" s="115">
+      <c r="F25" s="104">
         <v>46208</v>
       </c>
       <c r="G25" s="28"/>
@@ -3806,33 +3519,19 @@
       <c r="AV25" s="42"/>
       <c r="AW25" s="42"/>
       <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
-      <c r="BB25" s="42"/>
-      <c r="BC25" s="42"/>
-      <c r="BD25" s="42"/>
-      <c r="BE25" s="42"/>
-      <c r="BF25" s="42"/>
-      <c r="BG25" s="42"/>
-      <c r="BH25" s="42"/>
-      <c r="BI25" s="42"/>
-      <c r="BJ25" s="42"/>
-      <c r="BK25" s="42"/>
-      <c r="BL25" s="42"/>
-    </row>
-    <row r="26" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19"/>
       <c r="B26" s="79" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="80"/>
-      <c r="D26" s="107"/>
+      <c r="D26" s="98"/>
       <c r="E26" s="83"/>
-      <c r="F26" s="116"/>
+      <c r="F26" s="105"/>
       <c r="G26" s="84"/>
       <c r="H26" s="84" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I26" s="42"/>
@@ -3877,22 +3576,8 @@
       <c r="AV26" s="42"/>
       <c r="AW26" s="42"/>
       <c r="AX26" s="42"/>
-      <c r="AY26" s="42"/>
-      <c r="AZ26" s="42"/>
-      <c r="BA26" s="42"/>
-      <c r="BB26" s="42"/>
-      <c r="BC26" s="42"/>
-      <c r="BD26" s="42"/>
-      <c r="BE26" s="42"/>
-      <c r="BF26" s="42"/>
-      <c r="BG26" s="42"/>
-      <c r="BH26" s="42"/>
-      <c r="BI26" s="42"/>
-      <c r="BJ26" s="42"/>
-      <c r="BK26" s="42"/>
-      <c r="BL26" s="42"/>
-    </row>
-    <row r="27" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19"/>
       <c r="B27" s="85" t="s">
         <v>42</v>
@@ -3900,18 +3585,18 @@
       <c r="C27" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="110">
+      <c r="D27" s="99">
         <v>1</v>
       </c>
       <c r="E27" s="81">
         <v>46209</v>
       </c>
-      <c r="F27" s="117">
+      <c r="F27" s="106">
         <v>46210</v>
       </c>
       <c r="G27" s="28"/>
       <c r="H27" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="I27" s="42"/>
@@ -3956,22 +3641,8 @@
       <c r="AV27" s="42"/>
       <c r="AW27" s="42"/>
       <c r="AX27" s="42"/>
-      <c r="AY27" s="42"/>
-      <c r="AZ27" s="42"/>
-      <c r="BA27" s="42"/>
-      <c r="BB27" s="42"/>
-      <c r="BC27" s="42"/>
-      <c r="BD27" s="42"/>
-      <c r="BE27" s="42"/>
-      <c r="BF27" s="42"/>
-      <c r="BG27" s="42"/>
-      <c r="BH27" s="42"/>
-      <c r="BI27" s="42"/>
-      <c r="BJ27" s="42"/>
-      <c r="BK27" s="42"/>
-      <c r="BL27" s="42"/>
-    </row>
-    <row r="28" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19"/>
       <c r="B28" s="85" t="s">
         <v>43</v>
@@ -3979,18 +3650,18 @@
       <c r="C28" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="110">
+      <c r="D28" s="99">
         <v>1</v>
       </c>
       <c r="E28" s="81">
         <v>46210</v>
       </c>
-      <c r="F28" s="117">
+      <c r="F28" s="106">
         <v>46211</v>
       </c>
       <c r="G28" s="28"/>
       <c r="H28" s="82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="I28" s="42"/>
@@ -4035,22 +3706,8 @@
       <c r="AV28" s="42"/>
       <c r="AW28" s="42"/>
       <c r="AX28" s="42"/>
-      <c r="AY28" s="42"/>
-      <c r="AZ28" s="42"/>
-      <c r="BA28" s="42"/>
-      <c r="BB28" s="42"/>
-      <c r="BC28" s="42"/>
-      <c r="BD28" s="42"/>
-      <c r="BE28" s="42"/>
-      <c r="BF28" s="42"/>
-      <c r="BG28" s="42"/>
-      <c r="BH28" s="42"/>
-      <c r="BI28" s="42"/>
-      <c r="BJ28" s="42"/>
-      <c r="BK28" s="42"/>
-      <c r="BL28" s="42"/>
-    </row>
-    <row r="29" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19"/>
       <c r="B29" s="85" t="s">
         <v>66</v>
@@ -4058,13 +3715,13 @@
       <c r="C29" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="110">
+      <c r="D29" s="99">
         <v>1</v>
       </c>
       <c r="E29" s="81">
         <v>46211</v>
       </c>
-      <c r="F29" s="117">
+      <c r="F29" s="106">
         <v>46222</v>
       </c>
       <c r="G29" s="28"/>
@@ -4114,22 +3771,8 @@
       <c r="AV29" s="42"/>
       <c r="AW29" s="42"/>
       <c r="AX29" s="42"/>
-      <c r="AY29" s="42"/>
-      <c r="AZ29" s="42"/>
-      <c r="BA29" s="42"/>
-      <c r="BB29" s="42"/>
-      <c r="BC29" s="42"/>
-      <c r="BD29" s="42"/>
-      <c r="BE29" s="42"/>
-      <c r="BF29" s="42"/>
-      <c r="BG29" s="42"/>
-      <c r="BH29" s="42"/>
-      <c r="BI29" s="42"/>
-      <c r="BJ29" s="42"/>
-      <c r="BK29" s="42"/>
-      <c r="BL29" s="42"/>
-    </row>
-    <row r="30" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19"/>
       <c r="B30" s="85" t="s">
         <v>68</v>
@@ -4137,13 +3780,13 @@
       <c r="C30" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="110">
+      <c r="D30" s="99">
         <v>1</v>
       </c>
       <c r="E30" s="81">
         <v>46212</v>
       </c>
-      <c r="F30" s="117">
+      <c r="F30" s="106">
         <v>46222</v>
       </c>
       <c r="G30" s="28"/>
@@ -4193,22 +3836,8 @@
       <c r="AV30" s="42"/>
       <c r="AW30" s="42"/>
       <c r="AX30" s="42"/>
-      <c r="AY30" s="42"/>
-      <c r="AZ30" s="42"/>
-      <c r="BA30" s="42"/>
-      <c r="BB30" s="42"/>
-      <c r="BC30" s="42"/>
-      <c r="BD30" s="42"/>
-      <c r="BE30" s="42"/>
-      <c r="BF30" s="42"/>
-      <c r="BG30" s="42"/>
-      <c r="BH30" s="42"/>
-      <c r="BI30" s="42"/>
-      <c r="BJ30" s="42"/>
-      <c r="BK30" s="42"/>
-      <c r="BL30" s="42"/>
-    </row>
-    <row r="31" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19"/>
       <c r="B31" s="85" t="s">
         <v>69</v>
@@ -4216,13 +3845,13 @@
       <c r="C31" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="110">
+      <c r="D31" s="99">
         <v>1</v>
       </c>
       <c r="E31" s="81">
         <v>46213</v>
       </c>
-      <c r="F31" s="117">
+      <c r="F31" s="106">
         <v>46222</v>
       </c>
       <c r="G31" s="28"/>
@@ -4272,35 +3901,18 @@
       <c r="AV31" s="42"/>
       <c r="AW31" s="42"/>
       <c r="AX31" s="42"/>
-      <c r="AY31" s="42"/>
-      <c r="AZ31" s="42"/>
-      <c r="BA31" s="42"/>
-      <c r="BB31" s="42"/>
-      <c r="BC31" s="42"/>
-      <c r="BD31" s="42"/>
-      <c r="BE31" s="42"/>
-      <c r="BF31" s="42"/>
-      <c r="BG31" s="42"/>
-      <c r="BH31" s="42"/>
-      <c r="BI31" s="42"/>
-      <c r="BJ31" s="42"/>
-      <c r="BK31" s="42"/>
-      <c r="BL31" s="42"/>
-    </row>
-    <row r="32" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:50" s="30" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19"/>
-      <c r="B32" s="50" t="s">
+      <c r="B32" s="116" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="51"/>
-      <c r="D32" s="108"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
+      <c r="C32" s="116"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="116"/>
+      <c r="F32" s="116"/>
+      <c r="G32" s="116"/>
+      <c r="H32" s="117"/>
       <c r="I32" s="42"/>
       <c r="J32" s="42"/>
       <c r="K32" s="42"/>
@@ -4343,22 +3955,8 @@
       <c r="AV32" s="42"/>
       <c r="AW32" s="42"/>
       <c r="AX32" s="42"/>
-      <c r="AY32" s="42"/>
-      <c r="AZ32" s="42"/>
-      <c r="BA32" s="42"/>
-      <c r="BB32" s="42"/>
-      <c r="BC32" s="42"/>
-      <c r="BD32" s="42"/>
-      <c r="BE32" s="42"/>
-      <c r="BF32" s="42"/>
-      <c r="BG32" s="42"/>
-      <c r="BH32" s="42"/>
-      <c r="BI32" s="42"/>
-      <c r="BJ32" s="42"/>
-      <c r="BK32" s="42"/>
-      <c r="BL32" s="42"/>
-    </row>
-    <row r="33" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19"/>
       <c r="B33" s="57" t="s">
         <v>70</v>
@@ -4366,13 +3964,13 @@
       <c r="C33" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="110">
+      <c r="D33" s="99">
         <v>1</v>
       </c>
       <c r="E33" s="59">
         <v>46216</v>
       </c>
-      <c r="F33" s="111">
+      <c r="F33" s="100">
         <v>46222</v>
       </c>
       <c r="G33" s="28"/>
@@ -4408,9 +4006,9 @@
       <c r="AH33" s="42"/>
       <c r="AI33" s="42"/>
       <c r="AJ33" s="42"/>
-      <c r="AK33" s="89"/>
-      <c r="AL33" s="89"/>
-      <c r="AM33" s="89"/>
+      <c r="AK33" s="88"/>
+      <c r="AL33" s="88"/>
+      <c r="AM33" s="88"/>
       <c r="AN33" s="42"/>
       <c r="AO33" s="42"/>
       <c r="AP33" s="42"/>
@@ -4422,22 +4020,8 @@
       <c r="AV33" s="42"/>
       <c r="AW33" s="42"/>
       <c r="AX33" s="42"/>
-      <c r="AY33" s="42"/>
-      <c r="AZ33" s="42"/>
-      <c r="BA33" s="42"/>
-      <c r="BB33" s="42"/>
-      <c r="BC33" s="42"/>
-      <c r="BD33" s="42"/>
-      <c r="BE33" s="42"/>
-      <c r="BF33" s="42"/>
-      <c r="BG33" s="42"/>
-      <c r="BH33" s="42"/>
-      <c r="BI33" s="42"/>
-      <c r="BJ33" s="42"/>
-      <c r="BK33" s="42"/>
-      <c r="BL33" s="42"/>
-    </row>
-    <row r="34" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19"/>
       <c r="B34" s="57" t="s">
         <v>71</v>
@@ -4445,13 +4029,13 @@
       <c r="C34" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="110">
+      <c r="D34" s="99">
         <v>1</v>
       </c>
       <c r="E34" s="59">
         <v>46217</v>
       </c>
-      <c r="F34" s="111">
+      <c r="F34" s="100">
         <v>46222</v>
       </c>
       <c r="G34" s="28"/>
@@ -4488,9 +4072,9 @@
       <c r="AI34" s="42"/>
       <c r="AJ34" s="42"/>
       <c r="AK34" s="42"/>
-      <c r="AL34" s="89"/>
-      <c r="AM34" s="89"/>
-      <c r="AN34" s="89"/>
+      <c r="AL34" s="88"/>
+      <c r="AM34" s="88"/>
+      <c r="AN34" s="88"/>
       <c r="AO34" s="42"/>
       <c r="AP34" s="42"/>
       <c r="AQ34" s="42"/>
@@ -4501,22 +4085,8 @@
       <c r="AV34" s="42"/>
       <c r="AW34" s="42"/>
       <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
-      <c r="BB34" s="42"/>
-      <c r="BC34" s="42"/>
-      <c r="BD34" s="42"/>
-      <c r="BE34" s="42"/>
-      <c r="BF34" s="42"/>
-      <c r="BG34" s="42"/>
-      <c r="BH34" s="42"/>
-      <c r="BI34" s="42"/>
-      <c r="BJ34" s="42"/>
-      <c r="BK34" s="42"/>
-      <c r="BL34" s="42"/>
-    </row>
-    <row r="35" spans="1:64" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19"/>
       <c r="B35" s="57" t="s">
         <v>72</v>
@@ -4524,13 +4094,13 @@
       <c r="C35" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="110">
+      <c r="D35" s="99">
         <v>1</v>
       </c>
       <c r="E35" s="59">
         <v>46218</v>
       </c>
-      <c r="F35" s="111">
+      <c r="F35" s="100">
         <v>46222</v>
       </c>
       <c r="G35" s="28"/>
@@ -4568,9 +4138,9 @@
       <c r="AJ35" s="42"/>
       <c r="AK35" s="42"/>
       <c r="AL35" s="42"/>
-      <c r="AM35" s="89"/>
-      <c r="AN35" s="89"/>
-      <c r="AO35" s="89"/>
+      <c r="AM35" s="88"/>
+      <c r="AN35" s="88"/>
+      <c r="AO35" s="88"/>
       <c r="AP35" s="42"/>
       <c r="AQ35" s="42"/>
       <c r="AR35" s="42"/>
@@ -4580,22 +4150,8 @@
       <c r="AV35" s="42"/>
       <c r="AW35" s="42"/>
       <c r="AX35" s="42"/>
-      <c r="AY35" s="42"/>
-      <c r="AZ35" s="42"/>
-      <c r="BA35" s="42"/>
-      <c r="BB35" s="42"/>
-      <c r="BC35" s="42"/>
-      <c r="BD35" s="42"/>
-      <c r="BE35" s="42"/>
-      <c r="BF35" s="42"/>
-      <c r="BG35" s="42"/>
-      <c r="BH35" s="42"/>
-      <c r="BI35" s="42"/>
-      <c r="BJ35" s="42"/>
-      <c r="BK35" s="42"/>
-      <c r="BL35" s="42"/>
-    </row>
-    <row r="36" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19"/>
       <c r="B36" s="57" t="s">
         <v>73</v>
@@ -4603,13 +4159,13 @@
       <c r="C36" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="110">
+      <c r="D36" s="99">
         <v>1</v>
       </c>
       <c r="E36" s="59">
         <v>46219</v>
       </c>
-      <c r="F36" s="111">
+      <c r="F36" s="100">
         <v>46222</v>
       </c>
       <c r="G36" s="28"/>
@@ -4649,8 +4205,8 @@
       <c r="AL36" s="42"/>
       <c r="AM36" s="42"/>
       <c r="AN36" s="42"/>
-      <c r="AO36" s="89"/>
-      <c r="AP36" s="89"/>
+      <c r="AO36" s="88"/>
+      <c r="AP36" s="88"/>
       <c r="AQ36" s="42"/>
       <c r="AR36" s="42"/>
       <c r="AS36" s="42"/>
@@ -4659,22 +4215,8 @@
       <c r="AV36" s="42"/>
       <c r="AW36" s="42"/>
       <c r="AX36" s="42"/>
-      <c r="AY36" s="42"/>
-      <c r="AZ36" s="42"/>
-      <c r="BA36" s="42"/>
-      <c r="BB36" s="42"/>
-      <c r="BC36" s="42"/>
-      <c r="BD36" s="42"/>
-      <c r="BE36" s="42"/>
-      <c r="BF36" s="42"/>
-      <c r="BG36" s="42"/>
-      <c r="BH36" s="42"/>
-      <c r="BI36" s="42"/>
-      <c r="BJ36" s="42"/>
-      <c r="BK36" s="42"/>
-      <c r="BL36" s="42"/>
-    </row>
-    <row r="37" spans="1:64" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19"/>
       <c r="B37" s="57" t="s">
         <v>74</v>
@@ -4682,13 +4224,13 @@
       <c r="C37" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="110">
+      <c r="D37" s="99">
         <v>1</v>
       </c>
       <c r="E37" s="59">
         <v>46220</v>
       </c>
-      <c r="F37" s="111">
+      <c r="F37" s="100">
         <v>46222</v>
       </c>
       <c r="G37" s="28"/>
@@ -4729,8 +4271,8 @@
       <c r="AM37" s="42"/>
       <c r="AN37" s="42"/>
       <c r="AO37" s="42"/>
-      <c r="AP37" s="89"/>
-      <c r="AQ37" s="89"/>
+      <c r="AP37" s="88"/>
+      <c r="AQ37" s="88"/>
       <c r="AR37" s="42"/>
       <c r="AS37" s="42"/>
       <c r="AT37" s="42"/>
@@ -4738,32 +4280,18 @@
       <c r="AV37" s="42"/>
       <c r="AW37" s="42"/>
       <c r="AX37" s="42"/>
-      <c r="AY37" s="42"/>
-      <c r="AZ37" s="42"/>
-      <c r="BA37" s="42"/>
-      <c r="BB37" s="42"/>
-      <c r="BC37" s="42"/>
-      <c r="BD37" s="42"/>
-      <c r="BE37" s="42"/>
-      <c r="BF37" s="42"/>
-      <c r="BG37" s="42"/>
-      <c r="BH37" s="42"/>
-      <c r="BI37" s="42"/>
-      <c r="BJ37" s="42"/>
-      <c r="BK37" s="42"/>
-      <c r="BL37" s="42"/>
-    </row>
-    <row r="38" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:50" s="30" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19"/>
-      <c r="B38" s="90" t="s">
+      <c r="B38" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="94"/>
-      <c r="D38" s="109"/>
-      <c r="E38" s="95"/>
-      <c r="F38" s="119"/>
-      <c r="G38" s="96"/>
-      <c r="H38" s="96"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="119"/>
       <c r="I38" s="42"/>
       <c r="J38" s="42"/>
       <c r="K38" s="42"/>
@@ -4806,40 +4334,26 @@
       <c r="AV38" s="42"/>
       <c r="AW38" s="42"/>
       <c r="AX38" s="42"/>
-      <c r="AY38" s="42"/>
-      <c r="AZ38" s="42"/>
-      <c r="BA38" s="42"/>
-      <c r="BB38" s="42"/>
-      <c r="BC38" s="42"/>
-      <c r="BD38" s="42"/>
-      <c r="BE38" s="42"/>
-      <c r="BF38" s="42"/>
-      <c r="BG38" s="42"/>
-      <c r="BH38" s="42"/>
-      <c r="BI38" s="42"/>
-      <c r="BJ38" s="42"/>
-      <c r="BK38" s="42"/>
-      <c r="BL38" s="42"/>
-    </row>
-    <row r="39" spans="1:64" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19"/>
-      <c r="B39" s="97" t="s">
+      <c r="B39" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="91" t="s">
+      <c r="C39" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="110">
+      <c r="D39" s="99">
         <v>0.85</v>
       </c>
-      <c r="E39" s="92">
+      <c r="E39" s="90">
         <v>46222</v>
       </c>
-      <c r="F39" s="120">
+      <c r="F39" s="107">
         <v>46223</v>
       </c>
       <c r="G39" s="28"/>
-      <c r="H39" s="93">
+      <c r="H39" s="91">
         <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>2</v>
       </c>
@@ -4878,47 +4392,33 @@
       <c r="AO39" s="42"/>
       <c r="AP39" s="42"/>
       <c r="AQ39" s="42"/>
-      <c r="AR39" s="98"/>
-      <c r="AS39" s="98"/>
+      <c r="AR39" s="93"/>
+      <c r="AS39" s="93"/>
       <c r="AT39" s="42"/>
       <c r="AU39" s="42"/>
       <c r="AV39" s="42"/>
       <c r="AW39" s="42"/>
       <c r="AX39" s="42"/>
-      <c r="AY39" s="42"/>
-      <c r="AZ39" s="42"/>
-      <c r="BA39" s="42"/>
-      <c r="BB39" s="42"/>
-      <c r="BC39" s="42"/>
-      <c r="BD39" s="42"/>
-      <c r="BE39" s="42"/>
-      <c r="BF39" s="42"/>
-      <c r="BG39" s="42"/>
-      <c r="BH39" s="42"/>
-      <c r="BI39" s="42"/>
-      <c r="BJ39" s="42"/>
-      <c r="BK39" s="42"/>
-      <c r="BL39" s="42"/>
-    </row>
-    <row r="40" spans="1:64" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19"/>
-      <c r="B40" s="99" t="s">
+      <c r="B40" s="94" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="91" t="s">
+      <c r="C40" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="110">
+      <c r="D40" s="99">
         <v>0.65</v>
       </c>
-      <c r="E40" s="92">
+      <c r="E40" s="90">
         <v>46223</v>
       </c>
-      <c r="F40" s="120">
+      <c r="F40" s="107">
         <v>46225</v>
       </c>
       <c r="G40" s="28"/>
-      <c r="H40" s="93">
+      <c r="H40" s="91">
         <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>3</v>
       </c>
@@ -4957,47 +4457,33 @@
       <c r="AO40" s="42"/>
       <c r="AP40" s="42"/>
       <c r="AQ40" s="42"/>
-      <c r="AR40" s="98"/>
-      <c r="AS40" s="98"/>
-      <c r="AT40" s="98"/>
+      <c r="AR40" s="93"/>
+      <c r="AS40" s="93"/>
+      <c r="AT40" s="93"/>
       <c r="AU40" s="42"/>
       <c r="AV40" s="42"/>
       <c r="AW40" s="42"/>
       <c r="AX40" s="42"/>
-      <c r="AY40" s="42"/>
-      <c r="AZ40" s="42"/>
-      <c r="BA40" s="42"/>
-      <c r="BB40" s="42"/>
-      <c r="BC40" s="42"/>
-      <c r="BD40" s="42"/>
-      <c r="BE40" s="42"/>
-      <c r="BF40" s="42"/>
-      <c r="BG40" s="42"/>
-      <c r="BH40" s="42"/>
-      <c r="BI40" s="42"/>
-      <c r="BJ40" s="42"/>
-      <c r="BK40" s="42"/>
-      <c r="BL40" s="42"/>
-    </row>
-    <row r="41" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19"/>
-      <c r="B41" s="97" t="s">
+      <c r="B41" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="C41" s="91" t="s">
+      <c r="C41" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="110">
+      <c r="D41" s="99">
         <v>0.45</v>
       </c>
-      <c r="E41" s="92">
+      <c r="E41" s="90">
         <v>46224</v>
       </c>
-      <c r="F41" s="120">
+      <c r="F41" s="107">
         <v>46226</v>
       </c>
       <c r="G41" s="28"/>
-      <c r="H41" s="93">
+      <c r="H41" s="91">
         <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>3</v>
       </c>
@@ -5037,46 +4523,32 @@
       <c r="AP41" s="42"/>
       <c r="AQ41" s="42"/>
       <c r="AR41" s="42"/>
-      <c r="AS41" s="98"/>
-      <c r="AT41" s="98"/>
-      <c r="AU41" s="98"/>
+      <c r="AS41" s="93"/>
+      <c r="AT41" s="93"/>
+      <c r="AU41" s="93"/>
       <c r="AV41" s="42"/>
       <c r="AW41" s="42"/>
       <c r="AX41" s="42"/>
-      <c r="AY41" s="42"/>
-      <c r="AZ41" s="42"/>
-      <c r="BA41" s="42"/>
-      <c r="BB41" s="42"/>
-      <c r="BC41" s="42"/>
-      <c r="BD41" s="42"/>
-      <c r="BE41" s="42"/>
-      <c r="BF41" s="42"/>
-      <c r="BG41" s="42"/>
-      <c r="BH41" s="42"/>
-      <c r="BI41" s="42"/>
-      <c r="BJ41" s="42"/>
-      <c r="BK41" s="42"/>
-      <c r="BL41" s="42"/>
-    </row>
-    <row r="42" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19"/>
-      <c r="B42" s="97" t="s">
+      <c r="B42" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="C42" s="91" t="s">
+      <c r="C42" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="110">
+      <c r="D42" s="99">
         <v>0.4</v>
       </c>
-      <c r="E42" s="92">
+      <c r="E42" s="90">
         <v>46225</v>
       </c>
-      <c r="F42" s="120">
+      <c r="F42" s="107">
         <v>46227</v>
       </c>
       <c r="G42" s="28"/>
-      <c r="H42" s="93">
+      <c r="H42" s="91">
         <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>3</v>
       </c>
@@ -5117,45 +4589,31 @@
       <c r="AQ42" s="42"/>
       <c r="AR42" s="42"/>
       <c r="AS42" s="42"/>
-      <c r="AT42" s="98"/>
-      <c r="AU42" s="98"/>
-      <c r="AV42" s="98"/>
+      <c r="AT42" s="93"/>
+      <c r="AU42" s="93"/>
+      <c r="AV42" s="93"/>
       <c r="AW42" s="42"/>
       <c r="AX42" s="42"/>
-      <c r="AY42" s="42"/>
-      <c r="AZ42" s="42"/>
-      <c r="BA42" s="42"/>
-      <c r="BB42" s="42"/>
-      <c r="BC42" s="42"/>
-      <c r="BD42" s="42"/>
-      <c r="BE42" s="42"/>
-      <c r="BF42" s="42"/>
-      <c r="BG42" s="42"/>
-      <c r="BH42" s="42"/>
-      <c r="BI42" s="42"/>
-      <c r="BJ42" s="42"/>
-      <c r="BK42" s="42"/>
-      <c r="BL42" s="42"/>
-    </row>
-    <row r="43" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:50" s="30" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19"/>
-      <c r="B43" s="97" t="s">
+      <c r="B43" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="91" t="s">
+      <c r="C43" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="110">
+      <c r="D43" s="99">
         <v>0.1</v>
       </c>
-      <c r="E43" s="92">
+      <c r="E43" s="90">
         <v>46227</v>
       </c>
-      <c r="F43" s="120">
+      <c r="F43" s="107">
         <v>46227</v>
       </c>
       <c r="G43" s="28"/>
-      <c r="H43" s="93">
+      <c r="H43" s="91">
         <f>IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>1</v>
       </c>
@@ -5198,34 +4656,20 @@
       <c r="AS43" s="42"/>
       <c r="AT43" s="42"/>
       <c r="AU43" s="42"/>
-      <c r="AV43" s="98"/>
+      <c r="AV43" s="93"/>
       <c r="AW43" s="42"/>
       <c r="AX43" s="42"/>
-      <c r="AY43" s="42"/>
-      <c r="AZ43" s="42"/>
-      <c r="BA43" s="42"/>
-      <c r="BB43" s="42"/>
-      <c r="BC43" s="42"/>
-      <c r="BD43" s="42"/>
-      <c r="BE43" s="42"/>
-      <c r="BF43" s="42"/>
-      <c r="BG43" s="42"/>
-      <c r="BH43" s="42"/>
-      <c r="BI43" s="42"/>
-      <c r="BJ43" s="42"/>
-      <c r="BK43" s="42"/>
-      <c r="BL43" s="42"/>
-    </row>
-    <row r="44" spans="1:64" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19"/>
       <c r="B44" s="40"/>
       <c r="C44" s="39"/>
-      <c r="D44" s="110"/>
-      <c r="E44" s="121"/>
-      <c r="F44" s="122"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="109"/>
       <c r="G44" s="28"/>
       <c r="H44" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I44" s="42"/>
@@ -5270,22 +4714,8 @@
       <c r="AV44" s="42"/>
       <c r="AW44" s="42"/>
       <c r="AX44" s="42"/>
-      <c r="AY44" s="42"/>
-      <c r="AZ44" s="42"/>
-      <c r="BA44" s="42"/>
-      <c r="BB44" s="42"/>
-      <c r="BC44" s="42"/>
-      <c r="BD44" s="42"/>
-      <c r="BE44" s="42"/>
-      <c r="BF44" s="42"/>
-      <c r="BG44" s="42"/>
-      <c r="BH44" s="42"/>
-      <c r="BI44" s="42"/>
-      <c r="BJ44" s="42"/>
-      <c r="BK44" s="42"/>
-      <c r="BL44" s="42"/>
-    </row>
-    <row r="45" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19"/>
       <c r="B45" s="23"/>
       <c r="C45" s="24"/>
@@ -5294,7 +4724,7 @@
       <c r="F45" s="27"/>
       <c r="G45" s="28"/>
       <c r="H45" s="28" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I45" s="29"/>
@@ -5339,22 +4769,8 @@
       <c r="AV45" s="29"/>
       <c r="AW45" s="29"/>
       <c r="AX45" s="29"/>
-      <c r="AY45" s="29"/>
-      <c r="AZ45" s="29"/>
-      <c r="BA45" s="29"/>
-      <c r="BB45" s="29"/>
-      <c r="BC45" s="29"/>
-      <c r="BD45" s="29"/>
-      <c r="BE45" s="29"/>
-      <c r="BF45" s="29"/>
-      <c r="BG45" s="29"/>
-      <c r="BH45" s="29"/>
-      <c r="BI45" s="29"/>
-      <c r="BJ45" s="29"/>
-      <c r="BK45" s="29"/>
-      <c r="BL45" s="29"/>
-    </row>
-    <row r="46" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19"/>
       <c r="B46" s="23"/>
       <c r="C46" s="24"/>
@@ -5363,7 +4779,7 @@
       <c r="F46" s="27"/>
       <c r="G46" s="28"/>
       <c r="H46" s="28" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I46" s="29"/>
@@ -5408,22 +4824,8 @@
       <c r="AV46" s="29"/>
       <c r="AW46" s="29"/>
       <c r="AX46" s="29"/>
-      <c r="AY46" s="29"/>
-      <c r="AZ46" s="29"/>
-      <c r="BA46" s="29"/>
-      <c r="BB46" s="29"/>
-      <c r="BC46" s="29"/>
-      <c r="BD46" s="29"/>
-      <c r="BE46" s="29"/>
-      <c r="BF46" s="29"/>
-      <c r="BG46" s="29"/>
-      <c r="BH46" s="29"/>
-      <c r="BI46" s="29"/>
-      <c r="BJ46" s="29"/>
-      <c r="BK46" s="29"/>
-      <c r="BL46" s="29"/>
-    </row>
-    <row r="47" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19"/>
       <c r="B47" s="23"/>
       <c r="C47" s="24"/>
@@ -5432,7 +4834,7 @@
       <c r="F47" s="27"/>
       <c r="G47" s="28"/>
       <c r="H47" s="28" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I47" s="29"/>
@@ -5477,22 +4879,8 @@
       <c r="AV47" s="29"/>
       <c r="AW47" s="29"/>
       <c r="AX47" s="29"/>
-      <c r="AY47" s="29"/>
-      <c r="AZ47" s="29"/>
-      <c r="BA47" s="29"/>
-      <c r="BB47" s="29"/>
-      <c r="BC47" s="29"/>
-      <c r="BD47" s="29"/>
-      <c r="BE47" s="29"/>
-      <c r="BF47" s="29"/>
-      <c r="BG47" s="29"/>
-      <c r="BH47" s="29"/>
-      <c r="BI47" s="29"/>
-      <c r="BJ47" s="29"/>
-      <c r="BK47" s="29"/>
-      <c r="BL47" s="29"/>
-    </row>
-    <row r="48" spans="1:64" s="30" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:50" s="30" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19"/>
       <c r="B48" s="31"/>
       <c r="C48" s="32"/>
@@ -5501,7 +4889,7 @@
       <c r="F48" s="35"/>
       <c r="G48" s="36"/>
       <c r="H48" s="36" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I48" s="37"/>
@@ -5546,20 +4934,6 @@
       <c r="AV48" s="37"/>
       <c r="AW48" s="37"/>
       <c r="AX48" s="37"/>
-      <c r="AY48" s="37"/>
-      <c r="AZ48" s="37"/>
-      <c r="BA48" s="37"/>
-      <c r="BB48" s="37"/>
-      <c r="BC48" s="37"/>
-      <c r="BD48" s="37"/>
-      <c r="BE48" s="37"/>
-      <c r="BF48" s="37"/>
-      <c r="BG48" s="37"/>
-      <c r="BH48" s="37"/>
-      <c r="BI48" s="37"/>
-      <c r="BJ48" s="37"/>
-      <c r="BK48" s="37"/>
-      <c r="BL48" s="37"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="19"/>
@@ -5567,9 +4941,9 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
-    <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
@@ -5579,7 +4953,7 @@
     <mergeCell ref="T2:AK2"/>
     <mergeCell ref="AK4:AQ4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D7:D48">
+  <conditionalFormatting sqref="D7:D31 D33:D37 D39:D48">
     <cfRule type="dataBar" priority="12">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -5605,12 +4979,12 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:BL48">
+  <conditionalFormatting sqref="I5:AX48">
     <cfRule type="expression" dxfId="2" priority="27">
       <formula>AND(today&gt;=I$5,today&lt;I$5+1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:BL48">
+  <conditionalFormatting sqref="I7:AX48">
     <cfRule type="expression" dxfId="1" priority="25">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
@@ -5624,8 +4998,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -5654,7 +5029,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D7:D48</xm:sqref>
+          <xm:sqref>D7:D31 D33:D37 D39:D48</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5700,7 +5075,7 @@
       <c r="A4" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="104">
+      <c r="B4" s="95">
         <v>46188</v>
       </c>
     </row>
